--- a/exports/colleges/25602_iim-bangalore-indian-institute-of-management-bangalore.xlsx
+++ b/exports/colleges/25602_iim-bangalore-indian-institute-of-management-bangalore.xlsx
@@ -445,7 +445,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="172" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #14</t>
+          <t>Rank #2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.3 Lakhs</t>
+          <t>26.3 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CAT, GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>18 Apr - 30 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.5 Lakhs</t>
+          <t>4.5 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 60%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 17 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Arts</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Post Graduation + UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>26 July - 24 Jan 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -893,32 +893,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.68 Lakhs</t>
+          <t>33.68 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 50% + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>21 July - 20 Jan 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 with 60%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PGP</t>
+          <t>Post Graduate Programme in Business Analytics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PGP</t>
+          <t>Post Graduate Programme in Business Analytics</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 Lakhs - 26.3 Lakhs</t>
+          <t>26.3 Lakhs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>Bachelor of Business Administration [BBA] (Digital Enterprises Management)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>Bachelor of Business Administration [BBA] (Digital Enterprises Management)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 60%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EPGP</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EPGP</t>
+          <t>M.Phil/Ph.D in Arts</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.71 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation + UGC NET</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PGP Business Analytics</t>
+          <t>Executive Post Graduate Programme in Management [EPGPM]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PGP Business Analytics</t>
+          <t>Executive Post Graduate Programme in Management [EPGPM]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.3 Lakhs</t>
+          <t>33.68 Lakhs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50% + GMAT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BBA Digital Enterprises Management</t>
+          <t>Bachelor of Science [B.Sc] {Hons.}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BBA Digital Enterprises Management</t>
+          <t>Bachelor of Science [B.Sc] {Hons.}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.5 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 60%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EPGP General</t>
+          <t>PGP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EPGP General</t>
+          <t>PGP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.71 Lakhs</t>
+          <t>20 Lakhs - 26.3 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Time required to complete</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Time required to complete</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Time required to complete</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>4.5 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Time assigned</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time assigned</t>
+          <t>EPGP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Time assigned</t>
+          <t>EPGP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5 hours</t>
+          <t>33.71 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1498,57 +1498,367 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>PGP Business Analytics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PGP Business Analytics</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>26.3 Lakhs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BBA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BBA Digital Enterprises Management</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BBA Digital Enterprises Management</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EPGP General</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EPGP General</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>33.71 Lakhs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Time required to complete</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Time required to complete</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Time required to complete</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Time assigned</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Time assigned</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Time assigned</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.5 hours</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Marking scheme</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Marking scheme</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Marking scheme</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Correct answer - 1 mark, no negative marking</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>PG</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1700,12 +2010,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,15,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>34,88,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1715,7 +2025,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1740,7 +2050,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1779,7 +2089,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD Rank #14</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
